--- a/2022/North1/North1_Members_final.xlsx
+++ b/2022/North1/North1_Members_final.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>تيار القرار اللبناني</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
